--- a/ies-procesos/Calendario-Procesos-IES-2026.xlsx
+++ b/ies-procesos/Calendario-Procesos-IES-2026.xlsx
@@ -2198,13 +2198,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -2215,10 +2215,10 @@
       <c r="J27" s="27" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="27" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="27" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -2246,13 +2246,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -2266,7 +2266,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="27" t="n"/>
       <c r="Q28" s="27" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -2870,45 +2870,45 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="27" t="n"/>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
       <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="12" t="n"/>
-      <c r="U41" s="12" t="n"/>
-      <c r="V41" s="12" t="n"/>
-      <c r="W41" s="12" t="n"/>
-      <c r="X41" s="12" t="n"/>
-      <c r="Y41" s="12" t="n"/>
-      <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="12" t="n"/>
-      <c r="AB41" s="12" t="n"/>
-      <c r="AC41" s="12" t="n"/>
-      <c r="AD41" s="12" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-      <c r="AF41" s="12" t="n"/>
-      <c r="AG41" s="12" t="n"/>
-      <c r="AH41" s="12" t="n"/>
+      <c r="Q41" s="27" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="26" t="n"/>
+      <c r="V41" s="26" t="n"/>
+      <c r="W41" s="27" t="n"/>
+      <c r="X41" s="27" t="n"/>
+      <c r="Y41" s="26" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="26" t="n"/>
+      <c r="AC41" s="26" t="n"/>
+      <c r="AD41" s="27" t="n"/>
+      <c r="AE41" s="27" t="n"/>
+      <c r="AF41" s="26" t="n"/>
+      <c r="AG41" s="26" t="n"/>
+      <c r="AH41" s="26" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -2918,13 +2918,13 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E42" s="26" t="n"/>
@@ -2936,9 +2936,9 @@
       <c r="K42" s="26" t="n"/>
       <c r="L42" s="26" t="n"/>
       <c r="M42" s="26" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+      <c r="N42" s="26" t="n"/>
+      <c r="O42" s="26" t="n"/>
+      <c r="P42" s="27" t="n"/>
       <c r="Q42" s="27" t="n"/>
       <c r="R42" s="26" t="n"/>
       <c r="S42" s="26" t="n"/>
@@ -2952,9 +2952,9 @@
       <c r="AA42" s="26" t="n"/>
       <c r="AB42" s="26" t="n"/>
       <c r="AC42" s="26" t="n"/>
-      <c r="AD42" s="27" t="n"/>
-      <c r="AE42" s="27" t="n"/>
-      <c r="AF42" s="26" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
       <c r="AG42" s="26" t="n"/>
       <c r="AH42" s="26" t="n"/>
     </row>
@@ -3260,79 +3260,79 @@
         </is>
       </c>
       <c r="E50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S50" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="X50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC50" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="F50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O50" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R50" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S50" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC50" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD50" s="34" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
         <v>10</v>
       </c>
       <c r="AG50" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH50" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -4773,13 +4773,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -4790,10 +4790,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -4822,13 +4822,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -4842,7 +4842,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -5410,46 +5410,46 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr"/>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="27" t="n"/>
+      <c r="H40" s="27" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
       <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="12" t="n"/>
-      <c r="U40" s="12" t="n"/>
-      <c r="V40" s="12" t="n"/>
-      <c r="W40" s="12" t="n"/>
-      <c r="X40" s="12" t="n"/>
-      <c r="Y40" s="12" t="n"/>
-      <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="12" t="n"/>
-      <c r="AB40" s="12" t="n"/>
-      <c r="AC40" s="12" t="n"/>
-      <c r="AD40" s="12" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-      <c r="AF40" s="12" t="n"/>
-      <c r="AG40" s="12" t="n"/>
-      <c r="AH40" s="12" t="n"/>
-      <c r="AI40" s="12" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="27" t="n"/>
+      <c r="V40" s="27" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="27" t="n"/>
+      <c r="AC40" s="27" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
+      <c r="AI40" s="27" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -5459,13 +5459,13 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E41" s="26" t="n"/>
@@ -5477,9 +5477,9 @@
       <c r="K41" s="26" t="n"/>
       <c r="L41" s="26" t="n"/>
       <c r="M41" s="26" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+      <c r="N41" s="27" t="n"/>
+      <c r="O41" s="27" t="n"/>
+      <c r="P41" s="26" t="n"/>
       <c r="Q41" s="26" t="n"/>
       <c r="R41" s="26" t="n"/>
       <c r="S41" s="26" t="n"/>
@@ -5493,9 +5493,9 @@
       <c r="AA41" s="26" t="n"/>
       <c r="AB41" s="27" t="n"/>
       <c r="AC41" s="27" t="n"/>
-      <c r="AD41" s="26" t="n"/>
-      <c r="AE41" s="26" t="n"/>
-      <c r="AF41" s="26" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
       <c r="AG41" s="26" t="n"/>
       <c r="AH41" s="26" t="n"/>
       <c r="AI41" s="27" t="n"/>
@@ -5808,79 +5808,79 @@
         </is>
       </c>
       <c r="E49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="T49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC49" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O49" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="X49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD49" s="34" t="n">
         <v>10</v>
@@ -5892,13 +5892,13 @@
         <v>10</v>
       </c>
       <c r="AG49" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH49" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI49" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -7294,13 +7294,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="27" t="n"/>
@@ -7311,10 +7311,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="27" t="n"/>
       <c r="L27" s="27" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="27" t="n"/>
       <c r="S27" s="27" t="n"/>
@@ -7342,13 +7342,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="27" t="n"/>
@@ -7362,7 +7362,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="27" t="n"/>
       <c r="S28" s="27" t="n"/>
@@ -7966,45 +7966,45 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="27" t="n"/>
+      <c r="L41" s="27" t="n"/>
       <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="12" t="n"/>
-      <c r="U41" s="12" t="n"/>
-      <c r="V41" s="12" t="n"/>
-      <c r="W41" s="12" t="n"/>
-      <c r="X41" s="12" t="n"/>
-      <c r="Y41" s="12" t="n"/>
-      <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="12" t="n"/>
-      <c r="AB41" s="12" t="n"/>
-      <c r="AC41" s="12" t="n"/>
-      <c r="AD41" s="12" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-      <c r="AF41" s="12" t="n"/>
-      <c r="AG41" s="12" t="n"/>
-      <c r="AH41" s="12" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="27" t="n"/>
+      <c r="S41" s="27" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="26" t="n"/>
+      <c r="V41" s="26" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="27" t="n"/>
+      <c r="Z41" s="27" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="26" t="n"/>
+      <c r="AC41" s="26" t="n"/>
+      <c r="AD41" s="26" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="27" t="n"/>
+      <c r="AG41" s="27" t="n"/>
+      <c r="AH41" s="26" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -8014,13 +8014,13 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E42" s="27" t="n"/>
@@ -8032,9 +8032,9 @@
       <c r="K42" s="27" t="n"/>
       <c r="L42" s="27" t="n"/>
       <c r="M42" s="26" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+      <c r="N42" s="26" t="n"/>
+      <c r="O42" s="26" t="n"/>
+      <c r="P42" s="26" t="n"/>
       <c r="Q42" s="26" t="n"/>
       <c r="R42" s="27" t="n"/>
       <c r="S42" s="27" t="n"/>
@@ -8048,9 +8048,9 @@
       <c r="AA42" s="26" t="n"/>
       <c r="AB42" s="26" t="n"/>
       <c r="AC42" s="26" t="n"/>
-      <c r="AD42" s="26" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="27" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
       <c r="AG42" s="27" t="n"/>
       <c r="AH42" s="26" t="n"/>
     </row>
@@ -8356,79 +8356,79 @@
         </is>
       </c>
       <c r="E50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S50" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="X50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC50" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="F50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O50" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R50" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S50" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC50" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD50" s="34" t="n">
         <v>10</v>
@@ -8440,10 +8440,10 @@
         <v>10</v>
       </c>
       <c r="AG50" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH50" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -9869,13 +9869,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -9886,10 +9886,10 @@
       <c r="J27" s="27" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="27" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="27" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -9918,13 +9918,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -9938,7 +9938,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="27" t="n"/>
       <c r="Q28" s="27" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -10506,46 +10506,46 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr"/>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="27" t="n"/>
+      <c r="J40" s="27" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
       <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="12" t="n"/>
-      <c r="U40" s="12" t="n"/>
-      <c r="V40" s="12" t="n"/>
-      <c r="W40" s="12" t="n"/>
-      <c r="X40" s="12" t="n"/>
-      <c r="Y40" s="12" t="n"/>
-      <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="12" t="n"/>
-      <c r="AB40" s="12" t="n"/>
-      <c r="AC40" s="12" t="n"/>
-      <c r="AD40" s="12" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-      <c r="AF40" s="12" t="n"/>
-      <c r="AG40" s="12" t="n"/>
-      <c r="AH40" s="12" t="n"/>
-      <c r="AI40" s="12" t="n"/>
+      <c r="Q40" s="27" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="27" t="n"/>
+      <c r="X40" s="27" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="27" t="n"/>
+      <c r="AE40" s="27" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
+      <c r="AI40" s="26" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -10555,13 +10555,13 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E41" s="26" t="n"/>
@@ -10573,9 +10573,9 @@
       <c r="K41" s="26" t="n"/>
       <c r="L41" s="26" t="n"/>
       <c r="M41" s="26" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="27" t="n"/>
       <c r="Q41" s="27" t="n"/>
       <c r="R41" s="26" t="n"/>
       <c r="S41" s="26" t="n"/>
@@ -10589,9 +10589,9 @@
       <c r="AA41" s="26" t="n"/>
       <c r="AB41" s="26" t="n"/>
       <c r="AC41" s="26" t="n"/>
-      <c r="AD41" s="27" t="n"/>
-      <c r="AE41" s="27" t="n"/>
-      <c r="AF41" s="26" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
       <c r="AG41" s="26" t="n"/>
       <c r="AH41" s="26" t="n"/>
       <c r="AI41" s="26" t="n"/>
@@ -10904,79 +10904,79 @@
         </is>
       </c>
       <c r="E49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="T49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC49" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O49" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="X49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD49" s="34" t="n">
         <v>10</v>
@@ -10988,13 +10988,13 @@
         <v>10</v>
       </c>
       <c r="AG49" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH49" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI49" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -12420,13 +12420,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -12437,10 +12437,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -12469,13 +12469,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -12489,7 +12489,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -13106,46 +13106,46 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
       <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="12" t="n"/>
-      <c r="U41" s="12" t="n"/>
-      <c r="V41" s="12" t="n"/>
-      <c r="W41" s="12" t="n"/>
-      <c r="X41" s="12" t="n"/>
-      <c r="Y41" s="12" t="n"/>
-      <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="12" t="n"/>
-      <c r="AB41" s="12" t="n"/>
-      <c r="AC41" s="12" t="n"/>
-      <c r="AD41" s="12" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-      <c r="AF41" s="12" t="n"/>
-      <c r="AG41" s="12" t="n"/>
-      <c r="AH41" s="12" t="n"/>
-      <c r="AI41" s="12" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="27" t="n"/>
+      <c r="V41" s="27" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="26" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="27" t="n"/>
+      <c r="AC41" s="27" t="n"/>
+      <c r="AD41" s="26" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="26" t="n"/>
+      <c r="AG41" s="26" t="n"/>
+      <c r="AH41" s="26" t="n"/>
+      <c r="AI41" s="27" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -13155,13 +13155,13 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E42" s="26" t="n"/>
@@ -13173,9 +13173,9 @@
       <c r="K42" s="26" t="n"/>
       <c r="L42" s="26" t="n"/>
       <c r="M42" s="26" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+      <c r="N42" s="27" t="n"/>
+      <c r="O42" s="27" t="n"/>
+      <c r="P42" s="26" t="n"/>
       <c r="Q42" s="26" t="n"/>
       <c r="R42" s="26" t="n"/>
       <c r="S42" s="26" t="n"/>
@@ -13189,9 +13189,9 @@
       <c r="AA42" s="26" t="n"/>
       <c r="AB42" s="27" t="n"/>
       <c r="AC42" s="27" t="n"/>
-      <c r="AD42" s="26" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="26" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
       <c r="AG42" s="26" t="n"/>
       <c r="AH42" s="26" t="n"/>
       <c r="AI42" s="27" t="n"/>
@@ -13504,79 +13504,79 @@
         </is>
       </c>
       <c r="E50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S50" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="X50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC50" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="F50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O50" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R50" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S50" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC50" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD50" s="34" t="n">
         <v>10</v>
@@ -13588,13 +13588,13 @@
         <v>10</v>
       </c>
       <c r="AG50" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH50" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI50" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -14930,13 +14930,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="27" t="n"/>
@@ -14947,10 +14947,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="27" t="n"/>
       <c r="L27" s="27" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="27" t="n"/>
       <c r="S27" s="27" t="n"/>
@@ -14976,13 +14976,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="27" t="n"/>
@@ -14996,7 +14996,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="27" t="n"/>
       <c r="S28" s="27" t="n"/>
@@ -15528,43 +15528,43 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr"/>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="27" t="n"/>
+      <c r="L40" s="27" t="n"/>
       <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="12" t="n"/>
-      <c r="U40" s="12" t="n"/>
-      <c r="V40" s="12" t="n"/>
-      <c r="W40" s="12" t="n"/>
-      <c r="X40" s="12" t="n"/>
-      <c r="Y40" s="12" t="n"/>
-      <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="12" t="n"/>
-      <c r="AB40" s="12" t="n"/>
-      <c r="AC40" s="12" t="n"/>
-      <c r="AD40" s="12" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-      <c r="AF40" s="12" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="27" t="n"/>
+      <c r="S40" s="27" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="27" t="n"/>
+      <c r="Z40" s="27" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="27" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -15574,13 +15574,13 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E41" s="27" t="n"/>
@@ -15592,9 +15592,9 @@
       <c r="K41" s="27" t="n"/>
       <c r="L41" s="27" t="n"/>
       <c r="M41" s="26" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
       <c r="Q41" s="26" t="n"/>
       <c r="R41" s="27" t="n"/>
       <c r="S41" s="27" t="n"/>
@@ -15608,9 +15608,9 @@
       <c r="AA41" s="26" t="n"/>
       <c r="AB41" s="26" t="n"/>
       <c r="AC41" s="26" t="n"/>
-      <c r="AD41" s="26" t="n"/>
-      <c r="AE41" s="26" t="n"/>
-      <c r="AF41" s="27" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="31" t="inlineStr">
@@ -15902,79 +15902,79 @@
         </is>
       </c>
       <c r="E49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="T49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC49" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O49" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="X49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD49" s="34" t="n">
         <v>10</v>
@@ -17409,13 +17409,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="27" t="n"/>
@@ -17426,10 +17426,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="27" t="n"/>
       <c r="L27" s="27" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="27" t="n"/>
       <c r="S27" s="27" t="n"/>
@@ -17458,13 +17458,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="27" t="n"/>
@@ -17478,7 +17478,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="27" t="n"/>
       <c r="S28" s="27" t="n"/>
@@ -18095,46 +18095,46 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="27" t="n"/>
+      <c r="L41" s="27" t="n"/>
       <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="12" t="n"/>
-      <c r="U41" s="12" t="n"/>
-      <c r="V41" s="12" t="n"/>
-      <c r="W41" s="12" t="n"/>
-      <c r="X41" s="12" t="n"/>
-      <c r="Y41" s="12" t="n"/>
-      <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="12" t="n"/>
-      <c r="AB41" s="12" t="n"/>
-      <c r="AC41" s="12" t="n"/>
-      <c r="AD41" s="12" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-      <c r="AF41" s="12" t="n"/>
-      <c r="AG41" s="12" t="n"/>
-      <c r="AH41" s="12" t="n"/>
-      <c r="AI41" s="12" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="27" t="n"/>
+      <c r="S41" s="27" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="26" t="n"/>
+      <c r="V41" s="26" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="27" t="n"/>
+      <c r="Z41" s="27" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="26" t="n"/>
+      <c r="AC41" s="26" t="n"/>
+      <c r="AD41" s="26" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="27" t="n"/>
+      <c r="AG41" s="27" t="n"/>
+      <c r="AH41" s="26" t="n"/>
+      <c r="AI41" s="26" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -18144,13 +18144,13 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E42" s="27" t="n"/>
@@ -18162,9 +18162,9 @@
       <c r="K42" s="27" t="n"/>
       <c r="L42" s="27" t="n"/>
       <c r="M42" s="26" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+      <c r="N42" s="26" t="n"/>
+      <c r="O42" s="26" t="n"/>
+      <c r="P42" s="26" t="n"/>
       <c r="Q42" s="26" t="n"/>
       <c r="R42" s="27" t="n"/>
       <c r="S42" s="27" t="n"/>
@@ -18178,9 +18178,9 @@
       <c r="AA42" s="26" t="n"/>
       <c r="AB42" s="26" t="n"/>
       <c r="AC42" s="26" t="n"/>
-      <c r="AD42" s="26" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="27" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
       <c r="AG42" s="27" t="n"/>
       <c r="AH42" s="26" t="n"/>
       <c r="AI42" s="26" t="n"/>
@@ -18493,79 +18493,79 @@
         </is>
       </c>
       <c r="E50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S50" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="X50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC50" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="F50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O50" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R50" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S50" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC50" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD50" s="34" t="n">
         <v>10</v>
@@ -18577,13 +18577,13 @@
         <v>10</v>
       </c>
       <c r="AG50" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH50" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI50" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -19979,13 +19979,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -19996,10 +19996,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="27" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -20027,13 +20027,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -20047,7 +20047,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="27" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -20603,45 +20603,45 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr"/>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="27" t="n"/>
+      <c r="I40" s="27" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
       <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="12" t="n"/>
-      <c r="U40" s="12" t="n"/>
-      <c r="V40" s="12" t="n"/>
-      <c r="W40" s="12" t="n"/>
-      <c r="X40" s="12" t="n"/>
-      <c r="Y40" s="12" t="n"/>
-      <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="12" t="n"/>
-      <c r="AB40" s="12" t="n"/>
-      <c r="AC40" s="12" t="n"/>
-      <c r="AD40" s="12" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-      <c r="AF40" s="12" t="n"/>
-      <c r="AG40" s="12" t="n"/>
-      <c r="AH40" s="12" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="27" t="n"/>
+      <c r="W40" s="27" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="27" t="n"/>
+      <c r="AD40" s="27" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -20651,13 +20651,13 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E41" s="26" t="n"/>
@@ -20669,9 +20669,9 @@
       <c r="K41" s="26" t="n"/>
       <c r="L41" s="26" t="n"/>
       <c r="M41" s="26" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="27" t="n"/>
+      <c r="P41" s="27" t="n"/>
       <c r="Q41" s="26" t="n"/>
       <c r="R41" s="26" t="n"/>
       <c r="S41" s="26" t="n"/>
@@ -20685,9 +20685,9 @@
       <c r="AA41" s="26" t="n"/>
       <c r="AB41" s="26" t="n"/>
       <c r="AC41" s="27" t="n"/>
-      <c r="AD41" s="27" t="n"/>
-      <c r="AE41" s="26" t="n"/>
-      <c r="AF41" s="26" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
       <c r="AG41" s="26" t="n"/>
       <c r="AH41" s="26" t="n"/>
     </row>
@@ -20993,79 +20993,79 @@
         </is>
       </c>
       <c r="E49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="T49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC49" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O49" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="X49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD49" s="34" t="n">
         <v>10</v>
@@ -21077,10 +21077,10 @@
         <v>10</v>
       </c>
       <c r="AG49" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH49" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -22506,13 +22506,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -22523,10 +22523,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="27" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -22555,13 +22555,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -22575,7 +22575,7 @@
       <c r="M28" s="27" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -23192,46 +23192,46 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
       <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="12" t="n"/>
-      <c r="U41" s="12" t="n"/>
-      <c r="V41" s="12" t="n"/>
-      <c r="W41" s="12" t="n"/>
-      <c r="X41" s="12" t="n"/>
-      <c r="Y41" s="12" t="n"/>
-      <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="12" t="n"/>
-      <c r="AB41" s="12" t="n"/>
-      <c r="AC41" s="12" t="n"/>
-      <c r="AD41" s="12" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-      <c r="AF41" s="12" t="n"/>
-      <c r="AG41" s="12" t="n"/>
-      <c r="AH41" s="12" t="n"/>
-      <c r="AI41" s="12" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
+      <c r="T41" s="27" t="n"/>
+      <c r="U41" s="27" t="n"/>
+      <c r="V41" s="26" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="26" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="27" t="n"/>
+      <c r="AB41" s="27" t="n"/>
+      <c r="AC41" s="26" t="n"/>
+      <c r="AD41" s="26" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="26" t="n"/>
+      <c r="AG41" s="26" t="n"/>
+      <c r="AH41" s="27" t="n"/>
+      <c r="AI41" s="27" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -23241,13 +23241,13 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E42" s="26" t="n"/>
@@ -23259,9 +23259,9 @@
       <c r="K42" s="26" t="n"/>
       <c r="L42" s="26" t="n"/>
       <c r="M42" s="27" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+      <c r="N42" s="27" t="n"/>
+      <c r="O42" s="26" t="n"/>
+      <c r="P42" s="26" t="n"/>
       <c r="Q42" s="26" t="n"/>
       <c r="R42" s="26" t="n"/>
       <c r="S42" s="26" t="n"/>
@@ -23275,9 +23275,9 @@
       <c r="AA42" s="27" t="n"/>
       <c r="AB42" s="27" t="n"/>
       <c r="AC42" s="26" t="n"/>
-      <c r="AD42" s="26" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="26" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
       <c r="AG42" s="26" t="n"/>
       <c r="AH42" s="27" t="n"/>
       <c r="AI42" s="27" t="n"/>
@@ -23590,79 +23590,79 @@
         </is>
       </c>
       <c r="E50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S50" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="X50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC50" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="F50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O50" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R50" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S50" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC50" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD50" s="34" t="n">
         <v>10</v>
@@ -23674,13 +23674,13 @@
         <v>10</v>
       </c>
       <c r="AG50" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH50" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI50" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -25076,13 +25076,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -25093,10 +25093,10 @@
       <c r="J27" s="27" t="n"/>
       <c r="K27" s="27" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="27" t="n"/>
       <c r="R27" s="27" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -25124,13 +25124,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -25144,7 +25144,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="27" t="n"/>
       <c r="R28" s="27" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -25700,45 +25700,45 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr"/>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="27" t="n"/>
+      <c r="K40" s="27" t="n"/>
+      <c r="L40" s="26" t="n"/>
       <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="12" t="n"/>
-      <c r="U40" s="12" t="n"/>
-      <c r="V40" s="12" t="n"/>
-      <c r="W40" s="12" t="n"/>
-      <c r="X40" s="12" t="n"/>
-      <c r="Y40" s="12" t="n"/>
-      <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="12" t="n"/>
-      <c r="AB40" s="12" t="n"/>
-      <c r="AC40" s="12" t="n"/>
-      <c r="AD40" s="12" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-      <c r="AF40" s="12" t="n"/>
-      <c r="AG40" s="12" t="n"/>
-      <c r="AH40" s="12" t="n"/>
+      <c r="Q40" s="27" t="n"/>
+      <c r="R40" s="27" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="27" t="n"/>
+      <c r="Y40" s="27" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="27" t="n"/>
+      <c r="AF40" s="27" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -25748,13 +25748,13 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E41" s="26" t="n"/>
@@ -25766,9 +25766,9 @@
       <c r="K41" s="27" t="n"/>
       <c r="L41" s="26" t="n"/>
       <c r="M41" s="26" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
       <c r="Q41" s="27" t="n"/>
       <c r="R41" s="27" t="n"/>
       <c r="S41" s="26" t="n"/>
@@ -25782,9 +25782,9 @@
       <c r="AA41" s="26" t="n"/>
       <c r="AB41" s="26" t="n"/>
       <c r="AC41" s="26" t="n"/>
-      <c r="AD41" s="26" t="n"/>
-      <c r="AE41" s="27" t="n"/>
-      <c r="AF41" s="27" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
       <c r="AG41" s="26" t="n"/>
       <c r="AH41" s="26" t="n"/>
     </row>
@@ -26090,79 +26090,79 @@
         </is>
       </c>
       <c r="E49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="T49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC49" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O49" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="X49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD49" s="34" t="n">
         <v>10</v>
@@ -26174,10 +26174,10 @@
         <v>10</v>
       </c>
       <c r="AG49" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH49" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -27603,13 +27603,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="26" t="n"/>
@@ -27620,10 +27620,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="27" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="26" t="n"/>
@@ -27652,13 +27652,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -27672,7 +27672,7 @@
       <c r="M28" s="26" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="27" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="26" t="n"/>
@@ -28289,46 +28289,46 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
       <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="12" t="n"/>
-      <c r="U41" s="12" t="n"/>
-      <c r="V41" s="12" t="n"/>
-      <c r="W41" s="12" t="n"/>
-      <c r="X41" s="12" t="n"/>
-      <c r="Y41" s="12" t="n"/>
-      <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="12" t="n"/>
-      <c r="AB41" s="12" t="n"/>
-      <c r="AC41" s="12" t="n"/>
-      <c r="AD41" s="12" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-      <c r="AF41" s="12" t="n"/>
-      <c r="AG41" s="12" t="n"/>
-      <c r="AH41" s="12" t="n"/>
-      <c r="AI41" s="12" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="26" t="n"/>
+      <c r="V41" s="27" t="n"/>
+      <c r="W41" s="27" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="26" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="26" t="n"/>
+      <c r="AC41" s="27" t="n"/>
+      <c r="AD41" s="27" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="26" t="n"/>
+      <c r="AG41" s="26" t="n"/>
+      <c r="AH41" s="26" t="n"/>
+      <c r="AI41" s="26" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -28338,13 +28338,13 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E42" s="26" t="n"/>
@@ -28356,9 +28356,9 @@
       <c r="K42" s="26" t="n"/>
       <c r="L42" s="26" t="n"/>
       <c r="M42" s="26" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+      <c r="N42" s="26" t="n"/>
+      <c r="O42" s="27" t="n"/>
+      <c r="P42" s="27" t="n"/>
       <c r="Q42" s="26" t="n"/>
       <c r="R42" s="26" t="n"/>
       <c r="S42" s="26" t="n"/>
@@ -28372,9 +28372,9 @@
       <c r="AA42" s="26" t="n"/>
       <c r="AB42" s="26" t="n"/>
       <c r="AC42" s="27" t="n"/>
-      <c r="AD42" s="27" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="26" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
       <c r="AG42" s="26" t="n"/>
       <c r="AH42" s="26" t="n"/>
       <c r="AI42" s="26" t="n"/>
@@ -28687,79 +28687,79 @@
         </is>
       </c>
       <c r="E50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S50" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="X50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC50" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="F50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O50" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q50" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R50" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S50" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB50" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC50" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD50" s="34" t="n">
         <v>10</v>
@@ -28771,13 +28771,13 @@
         <v>10</v>
       </c>
       <c r="AG50" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH50" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI50" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -30203,13 +30203,13 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cartera por vigencias y por tercero desplegable</t>
+          <t>Sesión con Beatriz — variación de ingresos para socios</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>10 - 11</t>
+          <t>9 - 12</t>
         </is>
       </c>
       <c r="E27" s="27" t="n"/>
@@ -30220,10 +30220,10 @@
       <c r="J27" s="26" t="n"/>
       <c r="K27" s="26" t="n"/>
       <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="26" t="n"/>
+      <c r="P27" s="11" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="27" t="n"/>
@@ -30252,13 +30252,13 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sesión con Beatriz — comentarios comerciales al informe</t>
+          <t>Cartera por vigencias y por tercero desplegable</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>10 - 11</t>
         </is>
       </c>
       <c r="E28" s="27" t="n"/>
@@ -30272,7 +30272,7 @@
       <c r="M28" s="27" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="26" t="n"/>
       <c r="Q28" s="26" t="n"/>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="27" t="n"/>
@@ -30840,46 +30840,46 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Insumos de facturación — cantidades, valores y tipos</t>
+          <t>Análisis de variación de ingresos — sesión con el Contador</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr"/>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Todo el mes</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
+          <t>9 - 12</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="27" t="n"/>
       <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="12" t="n"/>
-      <c r="U40" s="12" t="n"/>
-      <c r="V40" s="12" t="n"/>
-      <c r="W40" s="12" t="n"/>
-      <c r="X40" s="12" t="n"/>
-      <c r="Y40" s="12" t="n"/>
-      <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="12" t="n"/>
-      <c r="AB40" s="12" t="n"/>
-      <c r="AC40" s="12" t="n"/>
-      <c r="AD40" s="12" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-      <c r="AF40" s="12" t="n"/>
-      <c r="AG40" s="12" t="n"/>
-      <c r="AH40" s="12" t="n"/>
-      <c r="AI40" s="12" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="27" t="n"/>
+      <c r="T40" s="27" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="27" t="n"/>
+      <c r="AA40" s="27" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="27" t="n"/>
+      <c r="AH40" s="27" t="n"/>
+      <c r="AI40" s="26" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -30889,13 +30889,13 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Comentarios comerciales al informe — sesión con el Contador</t>
+          <t>Entrega del insumo de facturación — cierre del período</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr"/>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>10 - 12</t>
+          <t>26 - 28</t>
         </is>
       </c>
       <c r="E41" s="27" t="n"/>
@@ -30907,9 +30907,9 @@
       <c r="K41" s="26" t="n"/>
       <c r="L41" s="27" t="n"/>
       <c r="M41" s="27" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
       <c r="Q41" s="26" t="n"/>
       <c r="R41" s="26" t="n"/>
       <c r="S41" s="27" t="n"/>
@@ -30923,9 +30923,9 @@
       <c r="AA41" s="27" t="n"/>
       <c r="AB41" s="26" t="n"/>
       <c r="AC41" s="26" t="n"/>
-      <c r="AD41" s="26" t="n"/>
-      <c r="AE41" s="26" t="n"/>
-      <c r="AF41" s="26" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
       <c r="AG41" s="27" t="n"/>
       <c r="AH41" s="27" t="n"/>
       <c r="AI41" s="26" t="n"/>
@@ -31238,79 +31238,79 @@
         </is>
       </c>
       <c r="E49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="T49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC49" s="34" t="n">
         <v>9</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O49" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q49" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="X49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="34" t="n">
-        <v>10</v>
       </c>
       <c r="AD49" s="34" t="n">
         <v>10</v>
@@ -31322,13 +31322,13 @@
         <v>10</v>
       </c>
       <c r="AG49" s="34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH49" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI49" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
